--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44494</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>44908</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45954</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45538</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>46047</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46247</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45208</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45952</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>46030</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44963</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45342</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46113</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45678</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45877</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44996</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44494</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>45246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45342</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>46036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46070</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>46073</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>45258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45177</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44950</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45258</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45709</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45074</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46167</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45369</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>46090</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>46196</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>46036</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44463</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>46209</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45384</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>45541</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45230</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44589</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44587</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44798</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44469</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44713</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44606</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45526</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45497</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>44987</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44789</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45470</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44977</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>45184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45688</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45967</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45678</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>46020</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45541</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>46035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>46031</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44500</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>46029</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45666</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>46092</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46021</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45251</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>46128</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>46108</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45062</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45799</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45237</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44798</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45173</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45173</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45335</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45803</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>46170</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>44575</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44886</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44458</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44832</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44466</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44630</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44461</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44670</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44664</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44494</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44494</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44804</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>44832</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44532</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44781</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44805</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>44792</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>44579</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>44495</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45252</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45369</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>44785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45016</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45489</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45215</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45213</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44679</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>44837</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45425</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45534</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45534</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>44747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45246</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45569</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45559</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45559</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45015</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45586</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>45140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45110</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45110</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45308</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45536</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45536</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45260</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45163</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44824</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44613</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45580</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45239</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44992</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44992</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45281</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45475</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45693</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45656</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45670</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45477</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45264</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45447</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45099</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>44917</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45694</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44935</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45632</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45079</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45341</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45215</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45384</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44867</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>46060</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44704</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45644</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45117</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45369</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44494</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>46035</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45890</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45891</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45527</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45891</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45299</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45820</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>44610</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45813</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46065</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45565</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>44999</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45358</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45259</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>46029</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45536</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45223</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45223</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>46095</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>46044</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>46042</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>46071</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44487</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45437</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>46038</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45267</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45182</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44601</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>46055</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>46065</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45939</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>46049</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46080</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44977</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>44529</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45607</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>46153</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45116</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45952</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>46131</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45954</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45139</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45954</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45958</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45958</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>46151</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>46037</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45946</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45194</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46057</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45963</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45974</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>44732</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44498</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>46154</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45258</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45575</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45982</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45624</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45986</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44992</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>46159</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45617</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45692</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45261</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45742</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45512</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>46167</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>46002</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44942</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45232</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>44468</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>46020</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>46027</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>46029</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44992</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>46030</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>46030</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>46030</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>46035</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>46171</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45251</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>46171</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44879</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>46036</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>44494</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>46036</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>46036</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45671</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>46031</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>46031</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45411</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>46049</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>46047</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>46176</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>46176</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44493</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>46055</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45702</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>46058</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>46058</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>44987</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>46062</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>46043</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>46063</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>46064</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>46066</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>44537</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>46067</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44565</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>46048</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>46071</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>46071</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>46071</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>46073</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>46072</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45631</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>46182</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>46077</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45068</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>46076</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45477</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44755</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>46089</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>46087</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>45719</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46185</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45091</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>46103</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>46104</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>46103</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45401</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45273</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>46111</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45485</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46113</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45709</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>46115</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46119</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46245</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>45223</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44524</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>46095</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44837</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>46095</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>46095</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>45643</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45054</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>46034</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>45258</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45188</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>46250</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45542</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45076</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>46209</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45390</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44550</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44972</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45392</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>45617</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>46115</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45210</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45294</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>45146</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>44467</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>44889</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45405</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>46265</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>46265</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45569</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45163</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45163</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45436</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45692</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45819</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>45517</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>45607</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45709</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45736</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45068</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46238</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>46237</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45568</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46238</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45054</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45632</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45796</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45770</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45799</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>45798</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45803</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45804</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>45812</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45813</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45813</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45831</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45833</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>45517</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45861</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45873</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>45874</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45875</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45875</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45880</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45880</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45880</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45883</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45882</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45009</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>44686</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45009</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45636</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45173</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45378</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45509</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45173</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>44638</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45817</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>44963</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>44963</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44649</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44615</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>46110</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>46131</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>46136</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44494</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44552</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45538</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>46047</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45954</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46030</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45208</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45952</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44963</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45757</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>45342</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>45827</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>46113</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45369</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45940</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45722</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45751</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45251</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45877</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45678</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>46036</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45342</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>46073</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>45678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44494</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44996</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>45258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>46024</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>46090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44950</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45384</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45709</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46036</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>46167</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46209</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45177</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44799</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>46290</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>46290</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>45258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45687</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45074</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45369</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45541</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44589</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44587</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44798</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44469</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>45541</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>46020</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>46029</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44977</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>46035</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>46031</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45470</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>46029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>46092</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>46021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45497</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45967</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>46128</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>46108</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45688</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45062</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44798</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>46188</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45678</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44789</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45666</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45526</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45184</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>45090</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44987</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45173</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>44886</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44827</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>44623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44466</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44630</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44670</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44664</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44494</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44804</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44832</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44532</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>44781</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44792</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44742</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44579</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45512</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45223</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45719</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45232</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45411</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45384</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45117</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45139</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44494</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>46020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45110</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>46027</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45796</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>46030</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45294</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>46030</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46030</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>44942</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45485</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>46029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45770</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45798</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45489</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46036</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45890</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45632</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45891</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45891</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45569</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45799</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46047</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45475</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46031</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>46049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>46055</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44889</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45527</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45803</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46058</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46058</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46043</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44987</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>46064</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>46063</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>46066</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>44537</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>46070</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46048</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44565</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45804</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46067</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>46071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>46071</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>46072</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>46077</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44992</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>46076</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>46073</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45099</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45369</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45586</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>46087</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45202</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46089</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45213</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45264</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45939</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>44977</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>44755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45091</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45812</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44704</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45950</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46104</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46103</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>46103</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45251</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45952</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45559</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45559</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45015</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45068</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>46111</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>45954</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44732</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45954</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44785</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>46113</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>45958</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>46115</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45569</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>46119</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45580</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45946</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>44494</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45813</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45963</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45016</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45813</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45974</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44992</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>46095</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>46095</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45981</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45982</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45631</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45986</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>46095</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>45534</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45534</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45692</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46002</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45477</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45813</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>46034</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>46038</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45656</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>46071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46035</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>46060</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45215</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45644</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45670</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>46065</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>46029</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44487</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46044</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>46042</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>46095</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45259</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>46065</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>46080</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45831</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44601</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>46055</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45261</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>46049</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44929</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>44999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44837</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46131</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44468</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44917</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>45079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>46153</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45833</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>46151</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>46154</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45405</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>46057</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>46037</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>46159</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45536</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45542</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45517</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45110</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46167</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>44992</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>46171</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45861</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>46171</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45392</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>46176</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45536</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>46176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45260</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>46182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45401</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45116</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45163</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45873</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44493</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45694</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45875</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45875</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45223</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45874</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45188</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45880</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45341</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>44550</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45880</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44613</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45880</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45054</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45882</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45624</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45076</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>46209</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45223</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45617</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44610</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>46250</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45208</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45617</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45210</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45163</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45140</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46115</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44679</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44824</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>46265</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46265</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45239</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45299</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45182</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45258</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>46237</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45146</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>46238</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>44867</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46238</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45536</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>46286</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>44524</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46287</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45194</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46288</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44992</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45436</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46185</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45447</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46245</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45308</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44747</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45425</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>44467</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45477</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45692</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45742</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>44837</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45281</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>44529</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>44972</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44498</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45693</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45709</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44879</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45702</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45390</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45258</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45252</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44935</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45437</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45671</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45607</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45267</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45036</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45358</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45183</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45215</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45819</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45517</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45709</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45068</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45607</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45736</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45054</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45568</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45632</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44686</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44638</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45636</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45173</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45378</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45509</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45173</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45817</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44963</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44963</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>44649</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>44615</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>46110</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>46131</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>46136</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44494</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44552</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45538</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>46047</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45954</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46030</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45208</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45952</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44963</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45757</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>45342</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>45827</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>46113</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45369</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45940</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45722</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45751</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45251</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45877</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45678</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>46036</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>46070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45342</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>46073</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45475</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>45678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44494</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44996</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44705</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>45258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>46024</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>46090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44950</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45384</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45709</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46036</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>46167</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46209</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45177</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44799</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>46290</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>46290</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>45258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45687</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45074</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45369</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45541</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>45230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44589</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44587</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44798</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44469</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>45541</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>46020</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>46029</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44977</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>46035</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>46031</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45470</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>46029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>46092</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>46021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45497</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45967</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>46128</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>46108</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45688</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45062</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44798</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>46188</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45678</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44789</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45666</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45526</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45184</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>45090</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44987</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45173</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>44886</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44827</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>44623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44466</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44630</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44670</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44664</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44494</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44804</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44832</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44532</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>44781</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44792</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44742</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44579</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45512</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45223</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45719</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45232</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45411</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45384</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45117</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45139</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44494</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>46020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45110</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>46027</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45796</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>46030</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45294</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>46030</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46030</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>44942</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45485</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>46029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45770</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45798</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45489</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46036</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46036</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45890</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45632</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45891</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45891</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45569</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45799</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46047</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45475</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46031</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>46049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>46055</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44889</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45527</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45803</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46058</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46058</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46043</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44987</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>46064</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>46063</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>46066</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>44537</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>46070</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46048</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44565</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45804</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46067</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>46071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>46071</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>46072</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>46077</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44992</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>46076</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>46073</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45099</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45369</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45586</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>46087</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45202</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46089</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45213</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45264</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45939</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>44977</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>44755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45091</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45812</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44704</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45950</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46104</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46103</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>46103</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45251</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45952</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45559</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45559</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45015</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45068</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>46111</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>45954</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44732</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45954</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>44785</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>46113</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>45958</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>46115</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45569</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>46119</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45580</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45946</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>44494</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45813</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45963</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45016</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45813</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45974</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44992</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>46095</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>46095</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45981</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45982</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45631</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45986</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>46095</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>45534</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45534</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45692</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46002</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45477</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45813</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>46034</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>46038</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45656</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>46071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46035</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>46060</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45215</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45644</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45820</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45670</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>46065</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>46029</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44487</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46044</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>46042</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>46095</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45259</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>46065</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>46080</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45831</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44601</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>46055</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45261</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>46049</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44929</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>44999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44837</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46131</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44468</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44917</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>45079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>46153</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45833</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>46151</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>46154</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45405</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>46057</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>46037</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>46159</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45536</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45542</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45517</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45110</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46167</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>44992</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>46171</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45861</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>46171</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45392</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>46176</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45536</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>46176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45260</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>46182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45401</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45116</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45163</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45873</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44493</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45694</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45875</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45875</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45223</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45874</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45188</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45880</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45341</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>44550</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45880</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44613</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45880</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45054</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45882</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45624</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45076</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>46209</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45223</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45617</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44610</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>46250</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45208</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45617</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45210</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45163</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45140</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46115</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44679</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44824</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>46265</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46265</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45239</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45299</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45182</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45258</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>46237</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45146</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>46238</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>44867</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46238</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45536</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>46286</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>44524</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46287</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45194</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46288</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>46288</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44992</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45436</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46185</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45447</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46245</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45308</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44747</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45425</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>44467</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45477</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45692</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45742</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>44837</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45281</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>44529</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>44972</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44498</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45693</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45709</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44879</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45702</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45390</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45258</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45252</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44935</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45437</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45671</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45607</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45267</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45036</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45358</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45183</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45215</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45819</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45517</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45709</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45068</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45607</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45736</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45054</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45568</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45632</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44686</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44638</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45636</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45173</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45378</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45509</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45173</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45817</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44963</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44963</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>44649</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>44615</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>46110</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>46131</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>46136</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44494</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46047</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45954</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45538</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45940</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>46216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46247</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>46030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45952</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45208</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44963</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45342</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>46113</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45757</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45751</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>45678</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45877</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>45678</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44996</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44494</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45246</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45342</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>46073</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>45541</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>46290</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>46024</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45177</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45068</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>46090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45709</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44950</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>46036</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>46167</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45074</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45687</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45369</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>46209</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>44874</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>46290</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>45384</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45541</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44798</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44606</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>46020</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45470</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46035</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>46031</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45799</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>46029</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45526</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45090</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>46092</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45967</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44987</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>46128</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>44789</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>46108</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44977</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45688</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44798</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>46188</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45678</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45541</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44500</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45062</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45173</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44599</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44670</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44664</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44494</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44510</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44494</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44498</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44832</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44781</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44742</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44579</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45369</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45252</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45534</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45534</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45016</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45213</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44837</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44679</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45736</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45068</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45425</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>44747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>46002</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45565</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45569</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45586</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45568</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45559</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45559</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45015</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45140</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45054</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>46020</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45890</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45891</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45891</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46027</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45110</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45110</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45632</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>46029</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>46030</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>46030</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>46035</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45308</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>46036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45536</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45536</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45260</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45796</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44613</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>46031</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45770</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>46049</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>44824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>46047</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45803</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45804</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45580</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>46055</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45208</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>46058</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45929</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>46058</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>44987</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44992</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44992</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45281</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>46062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45475</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>46043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45693</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>46066</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44537</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>46067</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44565</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46048</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45656</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45939</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>46071</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46071</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>46070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46071</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45670</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45477</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46073</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46072</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>45167</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>46077</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>46076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45447</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45952</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45812</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45954</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45954</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45813</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45958</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>46089</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>46087</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45694</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45963</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44935</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45632</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45384</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>46103</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45079</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45813</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45974</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>46104</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>46103</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45978</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45981</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45341</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46111</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45982</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45215</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>46113</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>46115</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46119</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44867</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44704</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45117</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45369</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44494</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45833</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>46095</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>46095</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>46095</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45527</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45299</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44610</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45202</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>46034</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>46060</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45517</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44999</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45358</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45644</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45536</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46035</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45223</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45223</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45437</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45820</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45267</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45813</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46065</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45182</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45861</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45259</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46095</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46044</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44977</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46042</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46071</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44529</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>44487</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46038</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45873</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45607</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44601</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45116</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>46055</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>46065</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46049</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>46080</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45139</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>46153</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46131</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>46151</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>46057</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46154</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45036</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45194</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46159</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45874</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45875</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45875</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44732</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>44498</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46167</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45258</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45880</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45880</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45575</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45624</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45880</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46171</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46171</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44992</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45883</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45882</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>46176</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45617</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45692</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45261</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45742</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45512</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>46182</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44942</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45232</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>44992</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45251</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44879</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>44494</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46209</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45671</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45411</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46115</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>44493</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45702</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>46265</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>46265</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45631</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>45068</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>45477</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44755</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>46238</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46237</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46238</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45091</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45401</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46287</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45273</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46286</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45485</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46185</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>46288</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45709</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46288</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>46245</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>46250</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45223</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>44524</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>44837</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45643</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45054</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45258</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>46297</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45542</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46296</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45390</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>44550</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44972</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45392</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45617</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>45210</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45294</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44889</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45405</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45569</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45163</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45163</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45436</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45692</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45819</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>45517</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>45607</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45709</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>44686</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45636</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45173</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45378</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45509</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45173</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>44638</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>45817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>44963</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44963</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44649</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44615</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>46110</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46131</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46136</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44494</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>44908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46047</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45954</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45538</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45940</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>46216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46247</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>46030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45952</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45208</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44963</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45342</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>46113</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45757</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45722</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45751</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>45678</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45877</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>45678</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45251</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44996</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44494</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45246</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45342</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>46073</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>45541</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>46290</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>46024</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45177</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45068</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>46090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45709</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44950</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>46036</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>46167</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45074</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45687</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45369</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>46209</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>44874</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>46290</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>45384</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45541</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44798</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44606</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>46020</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45470</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46035</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>46031</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45799</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>46029</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45526</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45090</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>46092</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45967</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44987</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>46128</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>44789</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>46108</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44977</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45688</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44798</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>46188</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45678</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45541</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44500</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45062</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45173</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44599</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44670</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44664</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44494</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44510</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44494</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44498</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44832</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44781</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44742</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44579</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45369</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45252</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45534</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45534</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45016</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45213</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44837</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44679</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45736</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45068</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45425</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>44747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>46002</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45565</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45569</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45586</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45568</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45559</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45559</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45015</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45140</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45054</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>46020</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45890</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45891</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45891</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46027</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45110</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45110</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45632</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>46029</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>46030</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>46030</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>46035</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45308</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>46036</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45536</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45536</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45260</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45796</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44613</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>46031</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45770</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>46049</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>44824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>46047</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45803</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45804</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45580</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>46055</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45208</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>46058</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45929</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>46058</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>44987</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44992</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44992</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45281</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>46062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45475</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>46043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45693</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>46066</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44537</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>46067</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44565</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46048</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45656</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45939</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>46071</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46071</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>46070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46071</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45670</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45477</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46073</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46072</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>45167</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>46077</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>46076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45447</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45952</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45812</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45954</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45954</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45813</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45958</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>46089</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>46087</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45694</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45963</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44935</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45632</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45384</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>46103</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45079</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45813</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45974</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>46104</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>46103</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45978</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45981</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45341</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46111</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45982</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45215</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>46113</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>46115</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46119</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44867</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44704</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45117</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>45369</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44494</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45833</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>46095</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>46095</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>46095</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45527</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45299</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44610</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45202</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>46034</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>46060</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45517</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44999</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45358</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45644</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45536</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46035</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45223</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45223</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45437</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45820</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45267</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45813</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46065</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45182</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45861</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45259</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46095</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46044</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44977</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46042</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46071</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>44529</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>44487</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46038</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45873</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45607</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44601</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45116</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>46055</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>46065</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46049</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>46080</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45139</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>46153</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46131</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>46151</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>46057</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46154</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45036</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45194</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46159</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45874</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45875</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45875</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44732</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>44498</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46167</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45258</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45880</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45880</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45575</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45624</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45880</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46171</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46171</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44992</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45883</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45882</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>46176</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45617</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45692</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45261</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45742</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45512</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>46182</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44942</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45232</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>44992</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45251</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44879</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>44494</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46209</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45671</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45411</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46115</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>44493</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45702</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>46265</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>46265</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45631</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>45068</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>45477</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44755</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>46238</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46237</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46238</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45091</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45401</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46287</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45273</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46286</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45485</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46185</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>46288</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45709</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46288</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>46245</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>46250</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45223</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>44524</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>44837</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45643</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45054</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45258</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>46297</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45542</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46296</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45390</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>44550</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44972</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45392</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45617</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>45210</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45294</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44889</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45405</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45569</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45163</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45163</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45436</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45692</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45819</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>45517</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>45607</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45709</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>44686</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45636</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45173</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45378</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45509</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45173</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>44638</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>45817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>44963</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44963</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44649</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44615</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>46110</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46131</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46136</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44494</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>44908</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45790</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>46248</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45538</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45954</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>46047</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45940</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>46216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46247</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45208</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45952</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46030</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44963</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45827</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45342</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46113</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45678</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>45751</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45877</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45475</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>46036</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45342</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44996</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>46073</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>45541</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>46290</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45074</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45258</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45369</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45541</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>45384</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45177</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45709</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>46024</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46036</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45687</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45068</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>46090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>46167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46209</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46290</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>46196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44798</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45062</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45251</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>45541</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>44987</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44500</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44977</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45470</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45251</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45678</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45799</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45666</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45526</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45967</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>45237</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45184</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45688</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>46020</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>46108</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>46029</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45090</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>46031</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>46029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>46092</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>46021</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>46188</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45173</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44799</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44687</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44742</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44505</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44670</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44664</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44498</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44805</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44494</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44792</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44532</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44781</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44804</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44742</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44832</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45719</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45232</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44999</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45411</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44837</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44579</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44495</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44705</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44498</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45079</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45405</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45384</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45693</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45709</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44879</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45536</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45542</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45512</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45702</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45223</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45390</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45258</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45117</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45167</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45110</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45252</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45575</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45883</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44935</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45139</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45437</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>44494</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45110</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45671</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45565</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45294</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44942</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45607</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45392</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45890</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45485</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45891</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45891</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45267</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45036</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45358</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45632</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45569</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45536</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45215</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45475</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45915</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45517</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45709</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45401</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44889</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45527</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45116</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45068</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45163</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45163</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45607</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>44493</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45736</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45694</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45054</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45223</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45188</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44992</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45341</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45099</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45568</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44550</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>44613</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45929</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45643</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45369</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45929</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45796</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45054</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45586</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45624</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45770</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45798</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45213</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45799</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45803</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44977</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44755</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45804</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45076</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45091</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>44704</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45223</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45617</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44610</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45251</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45559</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45559</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45015</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45208</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45068</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45617</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45813</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45813</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44732</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44785</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45569</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45140</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45580</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45950</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44494</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45952</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44679</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45016</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>45954</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45958</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45954</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45958</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44992</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45946</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45833</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45631</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45963</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45517</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45974</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45273</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45246</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45299</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45534</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45534</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45861</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45692</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45182</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45369</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45978</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45477</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45656</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45873</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45875</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45875</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45874</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45880</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45880</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45880</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45215</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45258</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45882</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45981</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45670</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45982</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45146</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45986</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>46104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46103</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>46103</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44867</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>46111</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45536</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>46113</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>46115</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45261</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>46119</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44524</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45194</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>46002</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45436</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>46095</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>46095</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>45447</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>45308</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>46095</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44747</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45425</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>46020</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>46027</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>46030</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>46030</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46030</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>46029</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45477</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45813</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>46034</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>46036</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46036</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>46035</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46038</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>46071</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46035</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45692</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>46060</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45742</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45644</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45820</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>46047</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>46031</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>44837</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46065</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>46031</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44529</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>44972</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>46029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>46049</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>44487</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>46044</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>46042</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>46055</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46095</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>46058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>46058</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46043</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46062</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45259</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>46065</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44987</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46080</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>46064</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>44601</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>46055</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>46066</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>46049</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44537</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46070</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46048</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44565</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46067</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>46131</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46071</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>46071</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>46072</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>46077</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>46076</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>46073</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>46153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46151</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>46154</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>46057</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46037</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>46087</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>46089</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>46159</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>46167</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>46171</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>46171</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>46176</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>46176</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>46182</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>46209</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46115</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>46265</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>46265</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>46237</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>46238</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>46286</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46287</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>46288</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46288</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46185</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46250</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>46296</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>46297</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>46299</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>44686</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45009</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>44638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45636</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45173</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45378</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45509</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45173</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44963</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>44963</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44649</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>44615</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>46110</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46131</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>46136</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44494</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>44908</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45790</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>46248</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45538</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45954</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>46047</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45940</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>46216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46247</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45208</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45952</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46030</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44963</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45827</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45342</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46113</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45678</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>45751</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45877</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45475</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>46036</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45342</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44996</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>46070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>46073</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>45541</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>46290</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45074</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45258</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45369</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45541</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>45384</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45177</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45709</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>46024</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46036</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45687</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45068</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>46090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>46167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46209</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46290</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>46196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44798</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45062</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45251</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>45541</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>44987</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44500</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44977</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45470</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45251</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45678</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45799</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45666</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45526</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45967</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>45237</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45184</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45688</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>46020</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>46108</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>46029</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45090</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>46031</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>46029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>46092</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>46021</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>46188</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45173</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44799</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44687</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44742</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44505</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44670</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44664</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44498</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44805</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44494</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44792</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44532</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44781</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44804</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44742</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44832</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45719</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45232</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44999</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45411</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44837</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44579</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44495</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44705</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44498</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45079</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45405</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>45384</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45693</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45709</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44879</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45536</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45542</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45512</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45702</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45223</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45390</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45258</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45117</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45167</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45110</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45252</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45575</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45883</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44935</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45139</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45437</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>44494</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45110</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45671</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45565</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45294</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44942</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45607</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45392</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45890</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45485</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45891</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45891</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45267</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45036</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45358</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45632</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45569</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45536</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45215</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45475</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45915</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45517</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45709</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45401</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44889</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45527</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45116</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45068</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45163</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45163</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45607</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>44493</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45736</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45694</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45054</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45223</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45188</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44992</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45341</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45099</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45568</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44550</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>44613</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45929</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45643</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45369</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45929</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45796</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45054</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45586</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45624</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45770</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45798</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45213</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45264</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45799</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45803</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44977</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44755</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45804</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45076</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45091</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>44704</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45223</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45617</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44610</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45251</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45559</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45559</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45015</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45208</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45068</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45617</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45813</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45813</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44732</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44785</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45569</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45140</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45580</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45950</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44494</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45952</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44679</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45016</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>45954</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45958</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45954</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45958</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44992</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45946</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45833</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45631</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45963</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45517</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45974</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45273</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45246</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45299</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45534</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45534</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45861</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45692</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45182</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45369</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45978</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45477</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45656</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45873</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45875</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45875</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45874</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45880</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45880</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45880</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45215</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45258</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45882</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45981</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45670</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45982</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45146</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45986</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>46104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46103</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>46103</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44867</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>46111</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45536</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>46113</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>46115</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45261</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>46119</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44524</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45194</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>46002</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45436</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>46095</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>46095</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>45447</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>45308</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>46095</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44747</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45425</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>46020</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>46027</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>46030</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>46030</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>46030</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>46029</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45477</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45813</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>46034</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>46036</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46036</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>46035</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46038</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>46071</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46035</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45692</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>46060</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45742</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45644</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45820</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>46047</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>46031</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>44837</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46065</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>46031</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44529</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>44972</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>46029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>46049</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>44487</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>46044</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>46042</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>46055</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46095</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>46058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>46058</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46043</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46062</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45259</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>46065</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44987</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46080</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>46064</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>44601</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>46055</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>46066</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>46049</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44537</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46070</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46048</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44565</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46067</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>46131</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46071</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>46071</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>46072</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>46077</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>46076</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>46073</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>46153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46151</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>46154</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>46057</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46037</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>46087</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>46089</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>46159</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>46167</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>46171</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>46171</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>46176</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>46176</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>46182</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>46209</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46115</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>46265</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>46265</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>46237</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>46238</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>46286</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46287</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>46288</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46288</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46185</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46250</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>46296</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>46297</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>46299</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>44686</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45009</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>44638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45636</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45173</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45378</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45509</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45173</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44963</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>44963</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44649</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>44615</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>46110</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46131</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>46136</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44494</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>44908</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45954</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45538</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>46047</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45208</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45952</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>46030</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44963</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45342</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46113</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45877</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44996</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44494</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>45246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45342</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>46036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>46073</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>46070</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>45541</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>46290</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45177</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44950</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45709</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>46167</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45074</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>45687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46024</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45369</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>46090</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44874</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>46036</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>46209</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45384</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>46290</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>46290</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45541</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>44798</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>44606</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45251</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45497</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44987</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44789</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45470</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45967</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44977</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45184</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45688</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>46020</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>46031</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45678</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>46029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>46188</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45541</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46092</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>46021</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44500</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>46128</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45666</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46108</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45251</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45062</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45237</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45173</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44599</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44886</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44664</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>44670</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>44494</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44498</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44832</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44781</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44742</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44579</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>44705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45252</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45534</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45534</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>44929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45369</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45016</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45213</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44679</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44837</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45425</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45246</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45569</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45586</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45559</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45559</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45015</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>45140</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45110</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45110</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44747</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45536</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45536</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45308</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45260</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44613</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44824</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45580</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44992</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44992</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45693</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45656</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45264</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45670</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45477</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45167</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45099</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45447</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45694</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44935</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45632</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45384</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45079</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45341</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45882</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46060</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45215</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45644</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46035</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44867</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44704</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45820</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45117</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45369</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44494</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45890</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45891</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45891</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45813</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>46065</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45565</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>46029</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>46095</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>46044</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>46042</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46071</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44487</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46038</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45527</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45299</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44610</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45202</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44601</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>46065</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>44999</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>46080</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45358</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45536</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45223</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45223</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45437</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45929</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45929</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>46153</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>46131</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45939</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45267</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>46151</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>46037</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45182</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>46057</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46154</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45954</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>45954</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45958</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>44977</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44529</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>46159</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45963</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45607</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45116</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45974</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45139</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45978</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45981</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>46167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45982</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45036</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45194</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45986</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>44732</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>44498</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45258</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45575</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>46002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>46171</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46171</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45624</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44992</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46020</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45617</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45692</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45261</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46027</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46029</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45742</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45512</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>46030</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>46030</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>46176</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>46030</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>46035</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46176</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>46036</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>46036</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>46036</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>44942</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>46031</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46031</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>46049</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>46047</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>46055</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46182</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46058</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45232</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>46058</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44987</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>46062</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46043</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>46063</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>46064</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>46066</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44537</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>46067</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44565</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>46048</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>46071</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>46071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>46070</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>46071</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>46073</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>46072</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44992</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46077</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46076</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45251</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>44879</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44494</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>46089</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>46087</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45671</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45411</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>46103</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>46103</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44493</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45702</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>46111</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>46113</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>46115</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46119</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45631</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45068</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46095</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>45477</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46095</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46095</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44755</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45719</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>46034</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45091</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46209</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45401</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46115</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45273</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45485</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45709</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45223</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>44524</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44837</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>46238</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45643</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45054</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46237</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45258</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>46238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45188</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45542</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45076</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46287</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>46286</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46185</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>46288</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45390</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>44550</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>46288</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>44972</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45392</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45617</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46250</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45146</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>44889</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45405</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45569</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46297</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45163</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>46296</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45436</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45692</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45819</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45517</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45607</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45709</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45736</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45068</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45568</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45632</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45796</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45770</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>46275</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45799</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45798</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45803</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46265</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45804</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45812</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45813</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45813</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>46299</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>46245</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>46310</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45831</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45833</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45517</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45861</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45873</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45874</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45875</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45875</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>45880</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45880</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45880</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45883</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>44686</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>45009</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45636</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45173</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45378</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45509</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45173</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44638</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45817</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44963</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>44963</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>44649</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44615</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>46110</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>46131</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>46136</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>44958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>45539</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44552</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44494</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>44908</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45954</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45538</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>46047</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45208</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45952</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>46030</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44963</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45342</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46113</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>45678</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45877</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45751</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44996</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44494</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>45246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45342</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>46036</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>46073</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>46070</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>45541</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>46290</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45177</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44950</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45709</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>46167</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45074</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>45687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46024</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45369</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>46090</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44874</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>46036</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>46209</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45384</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>46290</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>46290</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45541</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>44798</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>44606</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45251</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45497</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44987</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44789</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45470</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45967</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44977</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45184</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45688</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>46020</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>46031</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45678</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>46029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>46188</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45541</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46092</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>46021</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44500</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>46128</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45666</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46108</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45251</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45062</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45237</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45173</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44599</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44886</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44664</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>44670</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>44494</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44498</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44832</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44781</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44742</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44579</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>44705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45252</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45534</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45534</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>44929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45369</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44785</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45016</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45213</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44679</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44837</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45425</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45246</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45569</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45586</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45559</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45559</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45015</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>45140</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45110</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45110</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44747</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45536</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45536</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45308</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45260</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44613</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44824</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45580</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44992</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44992</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45693</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45656</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45264</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45670</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45477</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45167</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45099</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45447</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45694</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44935</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45632</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45384</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45079</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45341</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45882</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46060</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45215</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45644</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46035</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44867</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44704</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45820</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45117</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45369</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44494</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45890</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45891</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45891</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45813</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>46065</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45565</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>46029</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>46095</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>46044</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>46042</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46071</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44487</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46038</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45527</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45299</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44610</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45202</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44601</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>46065</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>44999</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>46080</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45358</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45536</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45223</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45223</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45437</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45929</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45929</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>46153</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>46131</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45939</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45267</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>46151</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>46037</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45182</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45950</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>46057</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46154</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45954</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>45954</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45958</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>44977</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44529</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>46159</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45963</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45607</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45116</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45974</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45139</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45978</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45981</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>46167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45982</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45036</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45194</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45986</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>44732</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>44498</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45258</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45575</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>46002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>46171</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46171</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45624</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44992</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46020</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45617</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45692</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45261</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46027</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46029</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45742</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45512</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>46030</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>46030</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>46176</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>46030</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>46035</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>46176</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>46036</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>46036</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>46036</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>44942</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>46031</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46031</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>46049</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>46047</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>46055</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46182</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46058</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45232</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>46058</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44987</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>46062</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46043</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>46063</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>46064</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>46066</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44537</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>46067</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44565</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>46048</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>46071</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>46071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>46070</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>46071</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>46073</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>46072</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44992</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46077</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46076</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45251</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>44879</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44494</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>46089</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>46087</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45671</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45411</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>46103</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>46103</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44493</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45702</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>46111</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>46113</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>46115</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46119</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45631</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45068</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46095</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>45477</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46095</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46095</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44755</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45719</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>46034</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45091</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46209</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45401</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46115</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45273</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45485</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45709</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45223</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>44524</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44837</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>46238</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45643</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45054</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46237</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45258</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>46238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45188</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45542</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45076</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46287</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>46286</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46185</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>46288</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45390</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>44550</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>46288</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>44972</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45392</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45617</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46250</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45146</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>44889</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45405</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45569</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46297</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45163</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>46296</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45436</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45692</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45819</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45517</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45607</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45709</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45736</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45068</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45568</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45632</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45796</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45770</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>46275</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45799</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45798</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45803</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46265</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45804</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45812</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45813</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45813</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>46299</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>46245</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>46310</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45831</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45833</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45517</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45861</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45873</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45874</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45875</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45875</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>45880</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45880</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45880</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45883</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>44686</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45009</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>45009</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45636</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45173</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45378</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45509</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45173</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44638</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45817</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44963</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>44963</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>44649</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44615</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>46110</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>46131</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>46136</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45539</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>44958</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44494</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44552</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45790</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44908</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45954</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>46047</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45538</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45952</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45208</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44963</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46113</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45827</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45342</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45751</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45877</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45678</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44996</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>46073</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45541</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>46290</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>45342</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45232</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>45475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45678</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45687</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>46167</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45074</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>45258</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45709</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45369</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46209</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45541</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>46024</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>46290</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>46290</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>46196</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45068</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>46090</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>46036</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44950</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45384</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45177</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>44799</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>44798</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45541</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45470</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>46188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44987</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45967</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46020</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>46029</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>46035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>46031</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45799</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>46092</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>46021</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>46128</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>44977</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>46108</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45497</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>45688</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45062</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44500</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45251</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44606</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45678</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44789</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45526</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45184</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45173</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>44623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>44799</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44670</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>44664</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>44494</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44498</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44832</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44781</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44742</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45565</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45447</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44495</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45890</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45883</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45512</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45891</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45891</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45308</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45223</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44747</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45425</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45719</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45232</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45411</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45477</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45915</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>46167</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45692</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45742</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46171</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44837</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45281</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44529</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45384</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>44498</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46176</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45117</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45693</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45709</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>46182</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44879</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45954</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45954</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45958</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45702</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45390</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45258</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45963</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45252</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45974</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>44935</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45437</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45978</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>45671</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45607</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45981</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45982</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>45986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>46209</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45036</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45358</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45139</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>46115</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45215</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>46002</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45819</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45517</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45709</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44494</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46237</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45068</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45607</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>46020</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>46238</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45110</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45736</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>46027</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>46030</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45054</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>46030</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>46030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>46238</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>46029</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>46036</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46036</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45568</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45632</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>46036</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>46035</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>46286</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45796</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46287</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>46288</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>46288</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>46047</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46031</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45770</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45798</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>46031</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>46185</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45799</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46049</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45803</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45804</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45294</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>46055</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>46058</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>46058</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46043</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45812</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44987</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46064</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44942</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45813</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>46063</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>46066</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44537</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>46070</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>46048</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>44565</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>46067</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>46071</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46071</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>46071</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>46250</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46296</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>46072</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>46077</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46076</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46073</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45831</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>46087</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>45833</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>46089</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46297</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45485</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45517</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45489</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>46104</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>46103</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>46103</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>46111</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45861</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>46113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>46115</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>46119</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45632</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45873</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45875</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>45875</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>45874</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45880</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45880</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45880</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>46275</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>46265</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45569</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45882</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>46095</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>46095</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>46265</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45475</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44889</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45527</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46095</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>46310</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>46299</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45813</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>46034</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>46314</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44992</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>46071</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45099</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>46245</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>46035</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46060</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45644</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45820</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45369</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>46065</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>46316</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45586</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>46029</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>46044</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45202</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46042</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>46095</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>46317</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45213</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45264</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>45259</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>46065</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>46080</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>44601</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>46055</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>46049</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>44977</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44755</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45091</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>46131</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44704</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46153</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45251</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45559</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45559</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46151</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46154</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45015</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45068</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>46057</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>46037</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44732</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44785</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>46159</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45569</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45580</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>44494</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45016</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>44992</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45631</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45534</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>45534</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45692</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45477</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45656</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45215</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45670</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45261</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44929</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44999</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44837</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44917</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45079</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45405</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45536</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45542</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45110</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44992</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45575</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45392</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45536</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45260</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45401</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45116</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45163</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45163</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44493</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45694</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45223</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45188</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45341</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>44550</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>44613</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45643</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45054</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45624</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45223</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44610</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45208</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45617</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45163</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45140</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44679</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>44824</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45273</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45246</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45239</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45299</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45182</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45369</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45258</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45146</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>44867</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>45536</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44524</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45194</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44992</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45436</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>44686</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>45009</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45009</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45009</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>44638</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45636</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45173</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45378</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45509</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45173</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45817</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44963</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44963</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44649</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>44615</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>46110</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>46131</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>46136</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>

--- a/Översikt BORLÄNGE.xlsx
+++ b/Översikt BORLÄNGE.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>45539</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>44958</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45105</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>44494</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44552</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44512</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45790</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44908</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46114</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45819</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45954</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>46047</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45538</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45902</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45952</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46030</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45208</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44963</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46113</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45827</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45342</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45751</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45877</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45678</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44996</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>46073</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45541</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>46290</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>45342</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45232</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>45475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45678</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44705</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45687</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>46167</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45074</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>45258</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45709</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45369</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46209</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45541</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>46024</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>46290</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>46290</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>46196</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45068</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>46090</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>46036</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44950</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45384</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45177</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>44799</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>44798</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45541</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45470</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>46188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44987</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45967</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46020</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>46029</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>46035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>46031</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45799</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>46092</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>46021</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>46128</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>44977</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>46108</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45497</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>45688</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45062</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44500</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45251</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44606</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45678</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44789</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45526</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45184</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45173</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45173</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45335</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>46170</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44575</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44827</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>44623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>44799</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44832</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44670</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>44664</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44494</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>44494</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44498</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44832</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44781</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44742</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45565</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45447</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44495</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45890</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45883</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45512</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45891</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45891</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45308</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45223</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44747</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45425</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45719</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45232</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45411</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45477</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45915</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>46167</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45692</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45742</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46171</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>44837</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45281</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44529</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45384</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>44498</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46176</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45117</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45693</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45709</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>46182</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44879</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45954</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45954</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45958</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45702</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45390</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45258</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45963</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45252</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45974</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>44935</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45437</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45978</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>45671</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45607</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45981</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45982</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>45986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>46209</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45036</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45358</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45139</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>46115</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45215</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>46002</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45819</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45517</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45709</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44494</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46237</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45068</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45607</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>46020</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>46238</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45110</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45736</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>46027</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>46030</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45054</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>46030</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>46030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>46238</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>46029</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>46036</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46036</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45568</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45632</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>46036</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>46035</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>46286</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45796</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46287</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>46288</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>46288</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>46047</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46031</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45770</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45798</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>46031</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>46185</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45799</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46049</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45803</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45804</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45294</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>46055</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>46058</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>46058</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46043</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45812</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44987</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46064</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44942</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45813</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>46063</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>46066</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44537</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>46070</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>46048</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>44565</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>46067</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>46071</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46071</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>46071</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>46250</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46296</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>46072</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>46077</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46076</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46073</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45831</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>46087</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>45833</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>46089</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46297</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45485</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45517</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45489</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>46104</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>46103</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>46103</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>46111</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45861</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>46113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>46115</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>46119</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45632</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45873</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45875</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>45875</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>45874</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45880</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45880</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45880</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>46275</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>46265</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45569</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45882</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>46095</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>46095</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>46265</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45475</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44889</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45527</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46095</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>46310</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>46299</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45813</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>46034</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>46314</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>46038</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44992</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>46071</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45099</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>46245</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>46035</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46060</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45644</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45820</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45369</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>46065</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>46316</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45586</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>46029</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>46044</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45202</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46042</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>46095</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>46317</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45213</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45264</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>45259</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>46065</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>46080</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>44601</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>46055</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>46049</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>44977</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44755</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45091</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>46131</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44704</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46153</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45251</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45559</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45559</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46151</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46154</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45015</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45068</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>46057</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>46037</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44732</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44785</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>46159</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45569</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45580</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>44494</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45016</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>44992</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45631</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45534</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>45534</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45692</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45477</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45656</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45215</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45670</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45261</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44929</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44999</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44837</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44917</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45079</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45405</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45536</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45542</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45110</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44992</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45575</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45392</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45536</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45260</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45401</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45116</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45163</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45163</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44493</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45694</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45223</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45188</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45341</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>44550</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>44613</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45643</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45054</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45624</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45223</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44610</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45208</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45617</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45163</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45140</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44679</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>44824</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45273</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45246</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45239</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45299</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45182</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45369</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45258</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45146</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>44867</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>45536</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44524</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45194</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44992</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45436</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>44686</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>45009</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45009</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45009</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>44638</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45636</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45173</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45378</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45509</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45173</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45817</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44963</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44963</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44649</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>44615</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>46110</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>46131</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>46136</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
